--- a/samples/ss_ksghn_ingest.xlsx
+++ b/samples/ss_ksghn_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,15 +758,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -797,7 +778,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -826,35 +806,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -883,23 +854,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>SST 40 MVA; outlet tower combined</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -915,7 +879,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -944,35 +907,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>2x300 MW</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1001,35 +955,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>U3 660 MW + U4 945 MW</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1058,23 +1003,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>single phi; 20/60/30 MVA + KTT Pertamina</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1090,7 +1028,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1119,23 +1056,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>single phi di GI Lomanis</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1151,7 +1081,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1180,35 +1109,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>2x60 MVA + KTT SBI</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1237,23 +1157,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>60/30 MVA</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1269,7 +1182,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1298,23 +1210,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>30/20/60/60/60 MVA</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1330,7 +1235,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1359,35 +1263,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>PLTA 8,3 MW</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1416,23 +1311,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1448,7 +1336,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1477,23 +1364,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1509,7 +1389,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1538,17 +1417,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>batas ke Subsistem Pemalang 1,2</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1564,13 +1437,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1599,23 +1470,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>3x60 MVA</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1631,7 +1495,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1660,23 +1523,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>PLTA Mrica; bay A1-A5 / B1-B4</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1692,7 +1548,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1721,23 +1576,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>30 MVA</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1753,7 +1601,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1782,23 +1629,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>single phi + single busbar; aset PT Geo Dipa Energi</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1814,7 +1654,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1843,23 +1682,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>74,5 MVA + 30 MVA</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1875,7 +1707,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1904,23 +1735,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>60/20/30 MVA + SMPOR 1 MW</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1936,7 +1760,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1965,23 +1788,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>30/60/60 MVA</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1997,7 +1813,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2026,23 +1841,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>30/60 MVA</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2058,7 +1866,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2087,17 +1894,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>batas ke GI Bantul / Subsistem Pedan</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -2123,7 +1924,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2152,35 +1952,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>16 MVA + PJKLN 1,4 MW + U1,U2 8 MW</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2209,35 +2000,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>20/30/60 MVA; arah BNJAR SS Tasik</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2266,35 +2048,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2401,7 +2174,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTU Cilacap U1,U2</t>
@@ -2422,7 +2194,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -2436,8 +2207,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2454,13 +2223,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Outlet PLTU Cilacap U3,U4</t>
@@ -2481,7 +2248,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -2495,8 +2261,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2513,7 +2277,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2544,7 +2307,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -2558,8 +2320,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2576,7 +2336,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2607,7 +2366,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -2621,8 +2379,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2639,7 +2395,6 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2670,7 +2425,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -2684,8 +2438,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2702,7 +2454,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2733,7 +2484,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -2747,8 +2497,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2765,7 +2513,6 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2796,7 +2543,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -2810,8 +2556,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2828,13 +2572,11 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Lomanis - Stara</t>
@@ -2855,7 +2597,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -2869,8 +2610,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2887,13 +2626,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTT Kesugihan - Rawalo</t>
@@ -2914,7 +2651,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -2928,8 +2664,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2946,7 +2680,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2977,7 +2710,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -2991,8 +2723,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3009,13 +2739,11 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT Kalibakal - Katenger</t>
@@ -3036,7 +2764,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -3050,8 +2777,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3068,7 +2793,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3099,7 +2823,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -3113,8 +2836,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3131,7 +2852,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3162,7 +2882,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -3176,8 +2895,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3194,13 +2911,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTT Balapulang - Kebasen</t>
@@ -3221,7 +2936,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -3235,8 +2949,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3253,13 +2965,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>SUTT Majenang - Sidareja</t>
@@ -3280,7 +2990,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -3294,8 +3003,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3312,13 +3019,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>SUTT Sidareja - Rawalo</t>
@@ -3339,7 +3044,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -3353,8 +3057,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3371,7 +3073,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3402,7 +3103,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -3416,8 +3116,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3434,7 +3132,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3465,7 +3162,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -3479,8 +3175,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3497,7 +3191,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3528,7 +3221,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -3542,8 +3234,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3560,7 +3250,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3591,7 +3280,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>1</v>
       </c>
@@ -3605,8 +3293,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3623,7 +3309,6 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3654,7 +3339,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -3668,8 +3352,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3686,7 +3368,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3717,7 +3398,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -3731,8 +3411,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3749,13 +3427,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>SUTT Wonosobo - Wadaslintang</t>
@@ -3776,7 +3452,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -3790,8 +3465,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3808,7 +3481,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3839,7 +3511,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -3853,8 +3524,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3871,7 +3540,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3902,7 +3570,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -3916,8 +3583,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3934,13 +3599,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>SUTT Kebumen - Purworejo</t>
@@ -3961,7 +3624,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -3975,8 +3637,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3993,7 +3653,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4024,7 +3683,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -4038,8 +3696,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4056,13 +3712,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>SUTT Wadaslintang - Purworejo</t>
@@ -4083,7 +3737,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -4097,8 +3750,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -4115,7 +3766,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4184,22 +3834,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan IBT 1,2 GITET Kesugihan&gt;60% sehingga N-1 tidak terpenuhi saat1 unit PLTU Cilacap tidak operasi</t>
+          <t>[N-1] Pembebanan IBT 1,2 GITET Kesugihan &gt;60% sehingga N-1 tidak terpenuhi saat 1 unit PLTU Cilacap tidak operasi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 1,2 Kesugihandengan total target sebesar 446MW.(Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW). 2.Pengoperasian PLTA Mrica. 3.Pergeseran beban GI ke subsistem lain</t>
+          <t>1. Sudah terpasang OLS IBT 1,2 Kesugihan dengan total target sebesar 446 MW.(Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW). 2. Pengoperasian PLTA Mrica. 3. Pergeseran beban GI ke subsistem lain</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JangkaMenengah: 1.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025- 2034, COD 2028). 2.Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025- 2034, COD 2028). 3.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028</t>
+          <t>Jangka Menengah: 1. Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025- 2034, COD 2028). 2. Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025- 2034, COD 2028). 3. Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028</t>
         </is>
       </c>
     </row>
@@ -4219,22 +3869,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1-1] Terjadi ekskursi tegangan dan mengakibatkan tripnya PLTA Mrica dan PLTP Dieng apabila SUTT 150 kV Rawalo- Purbalingga 1,2 atau Mrica-Wonosobo 1,2trip 2 sirkit (N-1-1/N-2) serta terjadi ekskursi tegangan pasokan bandara YIA</t>
+          <t>[N-1-1] Terjadi ekskursi tegangan dan mengakibatkan tripnya PLTA Mrica dan PLTP Dieng apabila SUTT 150 kV Rawalo- Purbalingga 1,2 atau Mrica -Wonosobo 1,2 trip 2 sirkit (N-1-1/N-2) serta terjadi ekskursi tegangan pasokan bandara YIA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.Terjadi ekskursi tegangan yang ekstrim sampai 120 kV di GI 150 kV Purbalingga atau Wates. 2.Kehilangan pasokan PLTP Dieng sebesar 50 MW akibat Drop tegangan apabila PLTA Mrica tidak beroperasi. 3.Berpotensi meningkatkan susut di Subsistem Kesugihan 1,2</t>
+          <t>1. Terjadi ekskursi tegangan yang ekstrim sampai 120 kV di GI 150 kV Purbalingga atau Wates. 2. Kehilangan pasokan PLTP Dieng sebesar 50 MW akibat Drop tegangan apabila PLTA Mrica tidak beroperasi. 3. Berpotensi meningkatkan susut di Subsistem Kesugihan 1,2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.Pekerjaanterencana dilakukanpadasaatb ebanrendahatausec araonlinedenganPD KB. 2.Mengurangidampak ekursitegangansaat pekerjaanoffline dengan mengoperasian PLTA Mrica minimal 2 unit dengan MVAR Maksimum serta memindahkanGI 150 kVTemanggung,Sec angdan WateskeSubsistem Ungaran/Pedan</t>
+          <t>1. Pekerjaanterencana dilakukanpadasaatb ebanrendahatausec araonlinedenganPD KB. 2. Mengurangidampak ekursitegangansaat pekerjaanoffline dengan mengoperasian PLTA Mrica minimal 2 unit dengan MVAR Maksimum serta memindahkan GI 150 kVTemanggung, Sec angdan Wates ke Subsistem Ungaran /Pedan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1.Usulan Pemasangan Defense Scheme UVLS SS Kesugihan. Rencana COD tahun 2026. 2.Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025- 2034, COD 2028)</t>
+          <t>Jangka Pendek: 1. Usulan Pemasangan Defense Scheme UVLS SS Kesugihan. Rencana COD tahun 2026. 2. Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025- 2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -4259,17 +3909,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan di salah satu ruas penghantar tersebut (N-1). 2.Terjadi ekskursi tegangan yang ekstrim sampai 130 kV di GI 150 kV Wates saat kondisi N-1- 1/N-2 pada ruas penghantar SUTT 150 kV Kesugihan- Gombong 1,2. Dampak 3.Fleksibilitasi operasi dan Keandalan berkurang</t>
+          <t>1. Terjadi Overload saat gangguan di salah satu ruas penghantar tersebut (N-1). 2. Terjadi ekskursi tegangan yang ekstrim sampai 130 kV di GI 150 kV Wates saat kondisi N-1- 1/N-2 pada ruas penghantar SUTT 150 kV Kesugihan- Gombong 1,2. Dampak 3. Fleksibilitasi operasi dan Keandalan berkurang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di SUTT 150 kV Kesugihan-Gombong total target sebesar 209 MW.(Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW). 2.Pekerjaanterencana dilakukanpadasaatb ebanrendahatausec araonlinedenganPD KB. Mitigasi 3.Mengurangidampak ekursitegangansaat pekerjaanofflineden ganmengoperasianP LTAMricaminimal2 unitdenganMVARM aksimumsertamemi ndahkanGI 150kVTemanggung, SecangdanWateske SubsistemUngaran/ Pedan</t>
+          <t>1. Sudah terpasang OLS di SUTT 150 kV Kesugihan-Gombong total target sebesar 209 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW). 2. Pekerjaanterencana dilakukanpadasaatb ebanrendahatausec araonlinedenganPD KB. Mitigasi 3. Mengurangidampak ekursitegangansaat pekerjaanofflineden ganmengoperasianP LTA Mricaminimal2 unit dengan MVARM aksimumsertamemi ndahkanGI 150 kVTemanggung, SecangdanWateske Subsistem Ungaran/ Pedan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Usulan Pemasangan Defense Scheme UVLS SS Kesugihan. Rencana COD tahun 2026. 2.Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025- 2034, COD 2028)</t>
+          <t>Jangka Pendek : 1. Usulan Pemasangan Defense Scheme UVLS SS Kesugihan. Rencana COD tahun 2026. 2. Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025- 2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -4289,7 +3939,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Konfigurasi SUTT 150 kV Kalibakal-Cilacap dan Rawalo - Kalibakalmasih singlephisehinggakurang andal</t>
+          <t>[BELUM_DITETAPKAN] Konfigurasi SUTT 150 kV Kalibakal-Cilacap dan Rawalo - Kalibakal masih single phi sehingga kurang andal</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4299,12 +3949,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.Pengaturan pekerjaan pemeliharaan pada saat beban rendah. 2.Pengaturan Splitting di GI 150 kV Kebasen, Brebes dipasok oleh Subsistem Mandirancan (UP2B Jabar). 3.Pembatasan pembebanan PLTU Cilacap 1,2</t>
+          <t>1. Pengaturan pekerjaan pemeliharaan pada saat beban rendah. 2. Pengaturan Splitting di GI 150 kV Kebasen, Brebes dipasok oleh Subsistem Mandirancan (UP2B Jabar). 3. Pembatasan pembebanan PLTU Cilacap 1,2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Uprating Kapasitor GI 150 kV Kebasen dari 25 MVAR menjadi 50 MVAR. Lalu kapasitor ex-GI 150 kV Kebasen 25 MVAR direlokasi ke GI 150 kV Balapulang, diusulkan COD 2027. (Usulan AI Tahun 2026 UIT JBT) 2.Rekonfigurasi SUTT 150 kV Kalibakal-Cilacap menjadi Rawalo- Kalibakal 2 sirkit (Double Phi) &amp; Cilacap-Rawalo menjadi 3 sirkit (RUPTL 2025-2034, COD 2027). Jangka Menengah: 3.Usulan baru penambahan SUTT Purbalingga- Purbalingga II/Belik, usulan COD Tahun 2029</t>
+          <t>Jangka Pendek : 1. Uprating Kapasitor GI 150 kV Kebasen dari 25 MVAR menjadi 50 MVAR. Lalu kapasitor ex-GI 150 kV Kebasen 25 MVAR direlokasi ke GI 150 kV Balapulang, diusulkan COD 2027. (Usulan AI Tahun 2026 UIT JBT) 2. Rekonfigurasi SUTT 150 kV Kalibakal-Cilacap menjadi Rawalo- Kalibakal 2 sirkit (Double Phi) &amp; Cilacap-Rawalo menjadi 3 sirkit (RUPTL 2025-2034, COD 2027). Jangka Menengah: 3. Usulan baru penambahan SUTT Purbalingga- Purbalingga II/Belik, usulan COD Tahun 2029</t>
         </is>
       </c>
     </row>
@@ -4324,22 +3974,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] 1.Konfigurasi SUTT 150 kV Kesugihan-Semen Nusantara &amp; Kesugihan-Lomanis masih single phi di GI Lomanis. 2.Terjadi pembebanan &gt;60% pada ruas Kesugihan-Lomanis apabila SUTT Kesugihan-Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi</t>
+          <t>[BELUM_DITETAPKAN] 1. Konfigurasi SUTT 150 kV Kesugihan-Semen Nusantara &amp; Kesugihan-Lomanis masih single phi di GI Lomanis. 2. Terjadi pembebanan &gt;60% pada ruas Kesugihan-Lomanis apabila SUTT Kesugihan-Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.Keandalan pasokan konsumen Pertamina berkurang. 2.TerjadiOverloadsaat gangguan 1 sirkit diruas tersebut. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Keandalan pasokan konsumen Pertamina berkurang. 2. TerjadiOverloadsaat gangguan 1 sirkit diruas tersebut. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di SUTT 150 kV Kesugihan-Lomanis sebesar 146 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW). 2.Pekerjaan diupayakan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS di SUTT 150 kV Kesugihan-Lomanis sebesar 146 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW). 2. Pekerjaan diupayakan saat beban rendah</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1.Rekonfigurasi SUTT 150 kV Kesugihan-Semen Nusantara menjadi Kesugihan-Lomanis dan Lomanis-Semen Nusantara 2 sirkit (Double Phi) (RUPTL 2025-2034, COD 2028). (Update: Komite Investasi) 2.Rekonduktoring SUTT 150 kV Kesugihan-Lomanis (RUPTL 2025-2034, COD 2027)</t>
+          <t>Jangka Pendek: 1. Rekonfigurasi SUTT 150 kV Kesugihan-Semen Nusantara menjadi Kesugihan-Lomanis dan Lomanis-Semen Nusantara 2 sirkit (Double Phi) (RUPTL 2025-2034, COD 2028). (Update: Komite Investasi) 2. Rekonduktoring SUTT 150 kV Kesugihan-Lomanis (RUPTL 2025-2034, COD 2027)</t>
         </is>
       </c>
     </row>
@@ -4364,17 +4014,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.Keandalan pasokan konsumen Pertamina berkurang. 2.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Keandalan pasokan konsumen Pertamina berkurang. 2. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di SUTT 150 kV Kesugihan-Semen Nusantara sebesar 146 MW. (RealisasiBPTa hun2025, 14 Oktober 2025-5721 MW). 2.Pekerjaan diupayakan dengan PDKB</t>
+          <t>1. Sudah terpasang OLS di SUTT 150 kV Kesugihan-Semen Nusantara sebesar 146 MW. (Realisasi BPTa hun2025, 14 Oktober 2025 -5721 MW). 2. Pekerjaan diupayakan dengan PDKB</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Rekonduktoring SUTT 150 kV Lomanis-Semen Nusantara (RUPTL 2025- 2034, COD 2028)</t>
+          <t>Jangka Pendek : Rekonduktoring SUTT 150 kV Lomanis-Semen Nusantara (RUPTL 2025- 2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -4399,17 +4049,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2.Potensi beban padam sebesar 100 MW saat kondisi N-2 di ruas penghantar SUTT 150 kV Kalibakal- Bumiayu. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2. Potensi beban padam sebesar 100 MW saat kondisi N-2 di ruas penghantar SUTT 150 kV Kalibakal- Bumiayu. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Kalibakal-Bumiayu total target sebesar 89MW. (Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW). 2.Pengaturan Splitting di GI 150 kV Kebasen, Brebes, dipasok oleh Subsistem Mandirancan (UP2B Jabar)</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Kalibakal-Bumiayu total target sebesar 89 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW). 2. Pengaturan Splitting di GI 150 kV Kebasen, Brebes, dipasok oleh Subsistem Mandirancan (UP2B Jabar)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Usulan uprating Kapasitor GI 150 kV Kebasen dari 25 MVAR menjadi 50 MVAR. Lalu kapasitor ex-GI 150 kV Kebasen 25 MVAR direlokasi ke GI 150 kV Balapulang, diusulkan COD 2027. (Usulan AI Tahun 2026 UIT JBT). 2.Rekonduktoring SUTT 150 kV Kalibakal-Bumiayu menjadi HTLSC, 1250 A per sirkit (RUPTL 2025- 2034, COD 2027). Jangka Panjang: 3.Usulan baru penambahan SUTT Purbalingga- Purbalingga II/Belik, usulan COD Tahun 2029</t>
+          <t>Jangka Pendek : 1. Usulan uprating Kapasitor GI 150 kV Kebasen dari 25 MVAR menjadi 50 MVAR. Lalu kapasitor ex-GI 150 kV Kebasen 25 MVAR direlokasi ke GI 150 kV Balapulang, diusulkan COD 2027. (Usulan AI Tahun 2026 UIT JBT). 2. Rekonduktoring SUTT 150 kV Kalibakal-Bumiayu menjadi HTLSC, 1250 A per sirkit (RUPTL 2025- 2034, COD 2027). Jangka Panjang: 3. Usulan baru penambahan SUTT Purbalingga- Purbalingga II/Belik, usulan COD Tahun 2029</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4084,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.Fleksibilitas operasi dan keandalan berkurang di PLTA Garung dan PLTP Dieng karena harus padam GI 150 kV Garung apabila ada pekerjaan atau gangguan pada Busbar di GI tersebut. 2.Padam PLTP Dieng dan PLTA Garung sebesar (±Total 130 MW) kondisi N-1-1</t>
+          <t>1. Fleksibilitas operasi dan keandalan berkurang di PLTA Garung dan PLTP Dieng karena harus padam GI 150 kV Garung apabila ada pekerjaan atau gangguan pada Busbar di GI tersebut. 2. Padam PLTP Dieng dan PLTA Garung sebesar (±Total 130 MW) kondisi N-1-1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4444,7 +4094,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JangkaMenengah: 1.RekonduktoringSUTT 150 kV Garung-Wonosobo, (RUPTL 2025-2034, COD 2027). 2.Usulan Rekonduktoring SUTT 150 kV Garung- Dieng-Wonosobo, (Belum masuk RUPTL) diusulkan COD 2027 (berbarengan dengan COD PLTP unit 2 Dieng). Note: Bay SUTT GI 150 kV Garung merupakan asset PT Geodipa Energi bersama dengan ruas penghantar dari PLTP Dieng hingga Ujung Usulan / Solusi penghantar di GI Wonosobo. Update terbaru: Penyerahan Asset Transmisi dan GI (Dieng- Garung) akan dilakukan pada saat COD PLTP Unit 2 Dieng pada Q2 Tahun 2027 dalam kondisi tidak dilakukan rekonduktoring dan uprating oleh PT Geo Dipa Energi</t>
+          <t>Jangka Menengah: 1. RekonduktoringSUTT 150 kV Garung-Wonosobo, (RUPTL 2025-2034, COD 2027). 2. Usulan Rekonduktoring SUTT 150 kV Garung- Dieng-Wonosobo, (Belum masuk RUPTL) diusulkan COD 2027 (berbarengan dengan COD PLTP unit 2 Dieng). Note: Bay SUTT GI 150 kV Garung merupakan asset PT Geodipa Energi bersama dengan ruas penghantar dari PLTP Dieng hingga Ujung Usulan / Solusi penghantar di GI Wonosobo. Update terbaru: Penyerahan Asset Transmisi dan GI (Dieng - Garung) akan dilakukan pada saat COD PLTP Unit 2 Dieng pada Q2 Tahun 2027 dalam kondisi tidak dilakukan rekonduktoring dan uprating oleh PT Geo Dipa Energi</t>
         </is>
       </c>
     </row>
@@ -4464,12 +4114,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] 1.GI 150 kV Garung (aset PT Geodipa Energi) beroperasi single phi dan single Busbar. 2.Tidak ada PMT 150 kV arah PLTA Garung</t>
+          <t>[BELUM_DITETAPKAN] 1. GI 150 kV Garung (aset PT Geodipa Energi) beroperasi single phi dan single Busbar. 2. Tidak ada PMT 150 kV arah PLTA Garung</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.Fleksibilitas operasi dan keandalan berkurang di PLTA Garung dan PLTP Dieng karena harus padam GI 150 kV Garung apabila ada pekerjaan atau gangguan pada Busbar di GI tersebut. 2.Kesulitan pemeliharaan Busbar di hari kerja</t>
+          <t>1. Fleksibilitas operasi dan keandalan berkurang di PLTA Garung dan PLTP Dieng karena harus padam GI 150 kV Garung apabila ada pekerjaan atau gangguan pada Busbar di GI tersebut. 2. Kesulitan pemeliharaan Busbar di hari kerja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4479,7 +4129,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1.Usulan pembangunan PMT 150 kV arah PLTA Garung. COD diusulkan Tahun 2026. Kajian operasisudah dikirim ke UIP2B. 2.Rekond &amp; Normalisasi GI 150 kV Garung (Double Phi Double Busbar) (RUPTL 2025-2034, COD 2027). 3.Pembangunan SUTT 150 kV Dieng -New Batang. Sesuai RUPTL 2025-2034 COD Tahun 2027. Note: Bay SUTT GI 150 kV Garung merupakan asset PT Geodipa Energi bersama dengan ruas penghantar dari PLTP Dieng hingga Ujung penghantar di GI Wonosobo. Update terbaru: Penyerahan Asset Transmisi dan GI (Dieng- Garung) akan dilakukan pada saat COD PLTP Unit 2 Dieng pada Q2 Tahun 2027 dalam kondisi tidak dilakukan rekonduktoring dan uprating oleh PT Geo Dipa Energi</t>
+          <t>Jangka Pendek: 1. Usulan pembangunan PMT 150 kV arah PLTA Garung. COD diusulkan Tahun 2026. Kajian operasi sudah dikirim ke UIP2B. 2.Rekond &amp; Normalisasi GI 150 kV Garung (Double Phi Double Busbar) (RUPTL 2025-2034, COD 2027). 3. Pembangunan SUTT 150 kV Dieng - New Batang. Sesuai RUPTL 2025-2034 COD Tahun 2027. Note: Bay SUTT GI 150 kV Garung merupakan asset PT Geodipa Energi bersama dengan ruas penghantar dari PLTP Dieng hingga Ujung penghantar di GI Wonosobo. Update terbaru: Penyerahan Asset Transmisi dan GI (Dieng - Garung) akan dilakukan pada saat COD PLTP Unit 2 Dieng pada Q2 Tahun 2027 dalam kondisi tidak dilakukan rekonduktoring dan uprating oleh PT Geo Dipa Energi</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4164,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jangka Panjang: Pembangunan SUTT 150 kV Dieng-New Batang. Sesuai RUPTL 2025-2034 COD Tahun 2027</t>
+          <t>Jangka Panjang : Pembangunan SUTT 150 kV Dieng -New Batang. Sesuai RUPTL 2025-2034 COD Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -4539,17 +4189,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2.Potensi beban padam sebesar 75 MW saat kondisi N-2 di ruas penghantar SUTT 150 kV Bumiayu- Balapulang. 3.Kesulitan pemeliharaan di hari kerja</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut. 2. Potensi beban padam sebesar 75 MW saat kondisi N-2 di ruas penghantar SUTT 150 kV Bumiayu- Balapulang. 3. Kesulitan pemeliharaan di hari kerja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Bumiayu-Balapulang sebesar 78 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW). 2.Pengaturan Splitting di GI 150 kV Kebasen, Brebes, dipasok oleh Subsistem Mandirancan (UP2B Jabar)</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Bumiayu-Balapulang sebesar 78 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW). 2. Pengaturan Splitting di GI 150 kV Kebasen, Brebes, dipasok oleh Subsistem Mandirancan (UP2B Jabar)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>JangkaMenengah: 1.Rekonduktoring SUTT 150 kV Bumiayu-Balapulang menjadi HTLSC, 1250 A per sirkit (RUPTL 2025- 2034, COD 2027). Jangka Menengah : 2.Usulan baru penambahan SUTT Purbalingga- Purbalingga II/Belik, usulan COD Tahun 2029</t>
+          <t>Jangka Menengah: 1. Rekonduktoring SUTT 150 kV Bumiayu-Balapulang menjadi HTLSC, 1250 A per sirkit (RUPTL 2025- 2034, COD 2027). Jangka Menengah : 2. Usulan baru penambahan SUTT Purbalingga- Purbalingga II/Belik, usulan COD Tahun 2029</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4219,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] 1.Outlet PLTU Cilacap (Cilacap-Rawalo 1,2, Cilacap-Kalibakal, Cilacap-Semen Nusantara) terletak pada tower combined sehingga tidak andal jika terjadi gangguan di ruas tersebut. 2.Intensitas pemeliharaan sangat tinggi karena kondisi polutan pada penghantar outlet PLTU Cilacap</t>
+          <t>[BELUM_DITETAPKAN] 1. Outlet PLTU Cilacap (Cilacap-Rawalo 1,2, Cilacap-Kalibakal, Cilacap-Semen Nusantara) terletak pada tower combined sehingga tidak andal jika terjadi gangguan di ruas tersebut. 2.Intensitas pemeliharaan sangat tinggi karena kondisi polutan pada penghantar outlet PLTU Cilacap</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4609,17 +4259,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.Terjadi ekskursi tegangan yang ekstrim sampai 120 kV di GI 150 kV Purbalingga atau Wates. 2.Kehilangan pasokan PLTP Dieng sebesar 50 MW akibat Drop tegangan apabila PLTA Mrica tidak beroperasi. 3.Berpotensi meningkatkan susut di Subsistem Kesugihan 1,2</t>
+          <t>1. Terjadi ekskursi tegangan yang ekstrim sampai 120 kV di GI 150 kV Purbalingga atau Wates. 2. Kehilangan pasokan PLTP Dieng sebesar 50 MW akibat Drop tegangan apabila PLTA Mrica tidak beroperasi. 3. Berpotensi meningkatkan susut di Subsistem Kesugihan 1,2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.Pekerjaanterencana dilakukanpadasaatb ebanrendahatausec araonlinedenganPD KB. 2.Mengurangidampak ekskursitegangansaa tpekerjaanoffline dengan mengoperasian PLTA Mrica minimal 2 unit dengan MVAR Maksimum serta memindahkanGI 150 kVTemanggung,Seca ngdan WateskeSubsistem Ungaran/ Pedan</t>
+          <t>1. Pekerjaanterencana dilakukanpadasaatb ebanrendahatausec araonlinedenganPD KB. 2. Mengurangidampak ekskursitegangansaa tpekerjaanoffline dengan mengoperasian PLTA Mrica minimal 2 unit dengan MVAR Maksimum serta memindahkan GI 150 kVTemanggung,Seca ngdan Wates ke Subsistem Ungaran / Pedan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Usulan Pemasangan Defense Scheme UVLS SS Kesugihan. Rencana COD tahun 2026. 2.Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025- 2034, COD 2028)</t>
+          <t>Jangka Pendek : 1. Usulan Pemasangan Defense Scheme UVLS SS Kesugihan. Rencana COD tahun 2026. 2. Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025- 2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4289,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT Kesugihan-Gombong 1,2 &gt; 60% sehingga tidak memenuhi N-1 apabila SUTT Rawalo - Purbalingga trip 2 sirkit/tidak operasi</t>
+          <t>[N-1] Pembebanan SUTT Kesugihan -Gombong 1,2 &gt; 60% sehingga tidak memenuhi N-1 apabila SUTT Rawalo - Purbalingga trip 2 sirkit/tidak operasi</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4649,12 +4299,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di SUTT 150 kV Kesugihan-Gombong 1,2. 2.Pekerjaan diupayakan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS di SUTT 150 kV Kesugihan-Gombong 1,2. 2. Pekerjaan diupayakan saat beban rendah</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025- 2034, COD 2028). 2.Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025- 2034, COD 2028). 3.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028</t>
+          <t>Jangka Pendek: 1. Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025- 2034, COD 2028). 2. Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025- 2034, COD 2028). 3. Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028</t>
         </is>
       </c>
     </row>
@@ -4674,22 +4324,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Terjadi pembebanan &gt;60% pada ruas Kesugihan - Lomanis apabila SUTT Kesugihan-Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi saat kondisi beban rendah dan PLTU Cilacap beroperasi maksimum</t>
+          <t>[BELUM_DITETAPKAN] Terjadi pembebanan &gt;60% pada ruas Kesugihan - Lomanis apabila SUTT Kesugihan -Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi saat kondisi beban rendah dan PLTU Cilacap beroperasi maksimum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.Keandalan pasokan konsumen Pertamina berkurang. 2.Terjadi Overload saat gangguan 1 sirkit di ruas tersebut. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Keandalan pasokan konsumen Pertamina berkurang. 2. Terjadi Overload saat gangguan 1 sirkit di ruas tersebut. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OGS di SUTT 150 kV Kesugihan-Lomanis. 2.Pengaturan pola operasi PLTU Cilacap pada saat beban rendah</t>
+          <t>1. Sudah terpasang OGS di SUTT 150 kV Kesugihan-Lomanis. 2. Pengaturan pola operasi PLTU Cilacap pada saat beban rendah</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Rekonfigurasi SUTT 150 kV Kesugihan-Semen Nusantara menjadi Kesugihan-Lomanis dan Lomanis-Semen Nusantara 2 sirkit (Double Phi) (RUPTL 2025-2034, COD 2027). (Update: Komite Investasi) 2.Rekonduktoring SUTT 150 kV Kesugihan-Lomanis (RUPTL 2025-2034, COD 2028)</t>
+          <t>Jangka Pendek: 1. Rekonfigurasi SUTT 150 kV Kesugihan-Semen Nusantara menjadi Kesugihan-Lomanis dan Lomanis-Semen Nusantara 2 sirkit (Double Phi) (RUPTL 2025-2034, COD 2027). (Update: Komite Investasi) 2. Rekonduktoring SUTT 150 kV Kesugihan-Lomanis (RUPTL 2025-2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -4709,22 +4359,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Terjadi pembebanan &gt;60% pada ruas Kesugihan - Semen Nusantara apabila SUTT Kesugihan- Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi saat kondisi beban rendah dan PLTU Cilacap beroperasi maksimum</t>
+          <t>[BELUM_DITETAPKAN] Terjadi pembebanan &gt;60% pada ruas Kesugihan - Semen Nusantara apabila SUTT Kesugihan - Rawalo trip 2 sirkit/tidak operasi sehingga N-1-2 tidak terpenuhi saat kondisi beban rendah dan PLTU Cilacap beroperasi maksimum</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.Keandalan pasokan konsumen Pertamina berkurang. 2.Terjadi Overload saat gangguan 1 sirkit di ruas tersebut. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Keandalan pasokan konsumen Pertamina berkurang. 2. Terjadi Overload saat gangguan 1 sirkit di ruas tersebut. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OGS di SUTT 150 kV Kesugihan-Semen Nusantara. 2.Pengaturan pola operasi PLTU Cilacap pada saat beban rendah</t>
+          <t>1. Sudah terpasang OGS di SUTT 150 kV Kesugihan-Semen Nusantara. 2. Pengaturan pola operasi PLTU Cilacap pada saat beban rendah</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Rekonfigurasi SUTT 150 kV Kesugihan-Semen Nusantara menjadi Kesugihan-Lomanis dan Lomanis-Semen Nusantara 2 sirkit (Double Phi) (RUPTL 2025-2034, COD 2027). (Update: Komite Investasi) 2.Rekonduktoring SUTT 150 kV Kesugihan-Lomanis (RUPTL 2025-2034, COD 2028)</t>
+          <t>Jangka Pendek: 1. Rekonfigurasi SUTT 150 kV Kesugihan-Semen Nusantara menjadi Kesugihan-Lomanis dan Lomanis-Semen Nusantara 2 sirkit (Double Phi) (RUPTL 2025-2034, COD 2027). (Update: Komite Investasi) 2. Rekonduktoring SUTT 150 kV Kesugihan-Lomanis (RUPTL 2025-2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -4749,17 +4399,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit di ruas tersebut. 2.Potensi padam meluas saat kondisi N-2 di ruas Dampak penghantar SUTT 150 kV Purworejo-Wates 1,2 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit di ruas tersebut. 2. Potensi padam meluas saat kondisi N-2 di ruas Dampak penghantar SUTT 150 kV Purworejo -Wates 1,2 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di SUTT 150 kV Purworejo - Wates 1,2. 2.Pekerjaan diupayakan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS di SUTT 150 kV Purworejo - Wates 1,2. 2. Pekerjaan diupayakan saat beban rendah</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025- 2034, COD 2028 Usulan / Solusi 2.Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025- 2034, COD 2028). 3.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028. Jangka Menengah : 4.RekonduktoringSUTT 150 kVPurworejo- WatesmenjadiHTLSC, 1250 A persirkit(RUPTL 2025-2034, COD 2029)</t>
+          <t>Jangka Pendek: 1. Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025- 2034, COD 2028 Usulan / Solusi 2. Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025- 2034, COD 2028). 3. Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028. Jangka Menengah : 4. RekonduktoringSUTT 150 kV Purworejo- Wates menjadiHTLSC, 1250 A per sirkit(RUPTL 2025-2034, COD 2029)</t>
         </is>
       </c>
     </row>
@@ -4779,22 +4429,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi pembebanan &gt; 60% pada ruas Kebumen- Gombong sehingga N-1 tidak terpenuhi jika memasok sampai GI Bantul</t>
+          <t>[N-1] Terjadi pembebanan &gt; 60% pada ruas Kebumen - Gombong sehingga N-1 tidak terpenuhi jika memasok sampai GI Bantul</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit di ruas tersebut. 2.Potensi padam meluas saat kondisi N-2 di ruas penghantar SUTT 150 kV Kebumen- Gombong 1,2 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit di ruas tersebut. 2. Potensi padam meluas saat kondisi N-2 di ruas penghantar SUTT 150 kV Kebumen- Gombong 1,2 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di SUTT 150 kV Kebumen-Gombong 1,2. 2.Pekerjaan diupayakan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS di SUTT 150 kV Kebumen -Gombong 1,2. 2. Pekerjaan diupayakan saat beban rendah</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025- 2034, COD 2028). 2.Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025- 2034, COD 2028). 3.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028</t>
+          <t>Jangka Pendek: 1. Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya (RUPTL 2025- 2034, COD 2028). 2. Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025- 2034, COD 2028). 3. Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028</t>
         </is>
       </c>
     </row>
